--- a/data/attendance/AMPHI_زهراوي_ادبي_2.xlsx
+++ b/data/attendance/AMPHI_زهراوي_ادبي_2.xlsx
@@ -325,7 +325,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="63">
   <si>
-    <t>زهراوي ادبي 2  |  AMPHI  |  BAC  |  - زهراوي</t>
+    <t>زهراوي ادبي 2  |  AMPHI  |  BAC  |  زهراوي</t>
   </si>
   <si>
     <t>class_id=10</t>

--- a/data/attendance/AMPHI_زهراوي_ادبي_2.xlsx
+++ b/data/attendance/AMPHI_زهراوي_ادبي_2.xlsx
@@ -20,301 +20,364 @@
     <comment ref="B5" authorId="0">
       <text>
         <r>
-          <t>student_id:6426c12c-9914-4ea0-b7f1-5244eafafb2f</t>
+          <t>student_id:17558c2a-1262-434a-97e3-56eca8a756b1</t>
         </r>
       </text>
     </comment>
     <comment ref="B6" authorId="0">
       <text>
         <r>
-          <t>student_id:e7d9bcdd-e3e8-4641-ae0d-cda5e2960d1e</t>
+          <t>student_id:1e892613-fb1a-4dd7-a7d8-8e2170bc0d4e</t>
         </r>
       </text>
     </comment>
     <comment ref="B7" authorId="0">
       <text>
         <r>
-          <t>student_id:a44bddd4-5e9b-48df-8363-f1eb6bc4e569</t>
+          <t>student_id:f1624681-c1a7-4737-b428-f389d7cdc975</t>
         </r>
       </text>
     </comment>
     <comment ref="B8" authorId="0">
       <text>
         <r>
-          <t>student_id:20c17701-f382-4410-bc0c-1a1389449416</t>
+          <t>student_id:0b7d12e6-cea4-4861-805e-d2a4cac3ec51</t>
         </r>
       </text>
     </comment>
     <comment ref="B9" authorId="0">
       <text>
         <r>
-          <t>student_id:d7ecc852-3b0f-4520-986c-d15db2a04963</t>
+          <t>student_id:ed42b87b-c4b3-4fff-98a5-a5156af6f689</t>
         </r>
       </text>
     </comment>
     <comment ref="B10" authorId="0">
       <text>
         <r>
-          <t>student_id:b3c3558c-a5d8-440b-bc19-7c52b4e1c69c</t>
+          <t>student_id:11e09847-4fe5-437d-89d7-80b103ce05a7</t>
         </r>
       </text>
     </comment>
     <comment ref="B11" authorId="0">
       <text>
         <r>
-          <t>student_id:4c5ce3bd-36b6-4064-8a09-76ceb462a076</t>
+          <t>student_id:b3ac5a70-f136-4fbd-ba38-0f00712e5362</t>
         </r>
       </text>
     </comment>
     <comment ref="B12" authorId="0">
       <text>
         <r>
-          <t>student_id:33cb11b7-8b00-4904-b996-f1227c382d09</t>
+          <t>student_id:99a6b5eb-f8ef-42f7-9d8d-450be69cbcf3</t>
         </r>
       </text>
     </comment>
     <comment ref="B13" authorId="0">
       <text>
         <r>
-          <t>student_id:295f2405-72af-4512-a2f1-8b9113087f41</t>
+          <t>student_id:ee2da73d-8c46-4332-a76e-81eac4fbf687</t>
         </r>
       </text>
     </comment>
     <comment ref="B14" authorId="0">
       <text>
         <r>
-          <t>student_id:8f128d13-49d0-4f02-a658-38fe32b1725c</t>
+          <t>student_id:44b5cb5d-f5f3-40f1-a42d-2a355c517e79</t>
         </r>
       </text>
     </comment>
     <comment ref="B15" authorId="0">
       <text>
         <r>
-          <t>student_id:c76f52da-0de8-4a28-8814-70f1e82c8474</t>
+          <t>student_id:be0915c3-3f34-422b-b71d-114f720f0ff9</t>
         </r>
       </text>
     </comment>
     <comment ref="B16" authorId="0">
       <text>
         <r>
-          <t>student_id:fefeb5ee-1473-4cfd-962f-f4c2ebb247e7</t>
+          <t>student_id:4a2c6443-9485-4beb-a1e1-79dba040809f</t>
         </r>
       </text>
     </comment>
     <comment ref="B17" authorId="0">
       <text>
         <r>
-          <t>student_id:434e7d1e-d873-4234-b3ea-44eeaafeb5fd</t>
+          <t>student_id:1937ad56-0494-4a16-8e8e-e38bd86eab28</t>
         </r>
       </text>
     </comment>
     <comment ref="B18" authorId="0">
       <text>
         <r>
-          <t>student_id:c2c983e6-937c-4481-95c3-efc31045def5</t>
+          <t>student_id:216b6e1b-5c35-446f-90eb-0b3769c3c745</t>
         </r>
       </text>
     </comment>
     <comment ref="B19" authorId="0">
       <text>
         <r>
-          <t>student_id:18118d82-eb2a-43ca-bdf0-652727a749dc</t>
+          <t>student_id:50589b50-f0a9-431d-b668-7693580bd713</t>
         </r>
       </text>
     </comment>
     <comment ref="B20" authorId="0">
       <text>
         <r>
-          <t>student_id:27809a85-82af-4f17-b718-f00b7858b166</t>
+          <t>student_id:f5e9ee37-b4b0-43ce-906e-abd54c789347</t>
         </r>
       </text>
     </comment>
     <comment ref="B21" authorId="0">
       <text>
         <r>
-          <t>student_id:503c048d-43a5-43aa-b0ad-47e33896bb69</t>
+          <t>student_id:fc3694ad-1ef1-4dfb-a3ff-ade61864b818</t>
         </r>
       </text>
     </comment>
     <comment ref="B22" authorId="0">
       <text>
         <r>
-          <t>student_id:af6af139-8443-4a22-98fa-ca24bb6d7421</t>
+          <t>student_id:ac87ac71-9fcb-4f92-bef9-33417995d6ec</t>
         </r>
       </text>
     </comment>
     <comment ref="B23" authorId="0">
       <text>
         <r>
-          <t>student_id:3a02c3b7-c2a8-4993-8462-7ec0357c7dc9</t>
+          <t>student_id:d4541bbb-072f-4861-a46c-930b232417f4</t>
         </r>
       </text>
     </comment>
     <comment ref="B24" authorId="0">
       <text>
         <r>
-          <t>student_id:1e142ba7-9bb4-4291-9a46-2e0ed2154f14</t>
+          <t>student_id:f8454c66-d041-4f71-854a-1897e725f844</t>
         </r>
       </text>
     </comment>
     <comment ref="B25" authorId="0">
       <text>
         <r>
-          <t>student_id:37b56e12-7b9c-4f10-80d9-5a35ca74cb2b</t>
+          <t>student_id:6f278547-d060-4238-9749-f231d68329be</t>
         </r>
       </text>
     </comment>
     <comment ref="B26" authorId="0">
       <text>
         <r>
-          <t>student_id:d212cabf-d615-4f73-bc96-98b53e40f558</t>
+          <t>student_id:635645e8-e183-4792-af28-708262cebe45</t>
         </r>
       </text>
     </comment>
     <comment ref="B27" authorId="0">
       <text>
         <r>
-          <t>student_id:26151b95-b87b-4986-adee-2eb4578897e8</t>
+          <t>student_id:faea8b09-9503-4c4c-814f-2de6581ee480</t>
         </r>
       </text>
     </comment>
     <comment ref="B28" authorId="0">
       <text>
         <r>
-          <t>student_id:0c46b9f2-181a-46e2-b65a-f631c3c046b8</t>
+          <t>student_id:f0f526ab-f4c2-4859-bd2a-a157bafd0908</t>
         </r>
       </text>
     </comment>
     <comment ref="B29" authorId="0">
       <text>
         <r>
-          <t>student_id:a005673f-a24d-426c-bfd1-2aa70aa1e64c</t>
+          <t>student_id:608cad76-2f39-4367-ac8a-aa8be715f677</t>
         </r>
       </text>
     </comment>
     <comment ref="B30" authorId="0">
       <text>
         <r>
-          <t>student_id:5eea1226-5e18-4868-bc55-079477720510</t>
+          <t>student_id:0ce281db-d0ce-4744-ad3e-b6f061a198a9</t>
         </r>
       </text>
     </comment>
     <comment ref="B31" authorId="0">
       <text>
         <r>
-          <t>student_id:3b51080d-2817-4be6-ae72-52955124b7c0</t>
+          <t>student_id:ec9b824b-718b-4fbd-9e89-239ba201a33e</t>
         </r>
       </text>
     </comment>
     <comment ref="B32" authorId="0">
       <text>
         <r>
-          <t>student_id:a3983c99-a8a6-4ba6-8c64-d363beee05bf</t>
+          <t>student_id:d0763c0b-bc02-4a69-82be-2fd3386f470a</t>
         </r>
       </text>
     </comment>
     <comment ref="B33" authorId="0">
       <text>
         <r>
-          <t>student_id:185fafa2-0d59-4375-bdee-8b02885bb665</t>
+          <t>student_id:78ea45ba-95ee-455a-a124-6c967b6f6953</t>
         </r>
       </text>
     </comment>
     <comment ref="B34" authorId="0">
       <text>
         <r>
-          <t>student_id:da7caeb8-8865-464f-bddb-adfee7ea1f45</t>
+          <t>student_id:3ebf1dfc-9076-4122-a2dc-43b6b1e9c0fe</t>
         </r>
       </text>
     </comment>
     <comment ref="B35" authorId="0">
       <text>
         <r>
-          <t>student_id:2623117b-a609-4918-90a4-adfd7640ca07</t>
+          <t>student_id:31fe298a-ac2e-453f-b6c1-d1745c5e3e59</t>
         </r>
       </text>
     </comment>
     <comment ref="B36" authorId="0">
       <text>
         <r>
-          <t>student_id:edf38fad-df61-4bd5-85fc-4b7e0f044142</t>
+          <t>student_id:d22b3e6b-1630-40f5-91b3-7b6fc7e4ad05</t>
         </r>
       </text>
     </comment>
     <comment ref="B37" authorId="0">
       <text>
         <r>
-          <t>student_id:44b73a35-1308-4786-9d5d-46db26780a3c</t>
+          <t>student_id:b2a65661-2ddd-4d8d-9070-9e268765452b</t>
         </r>
       </text>
     </comment>
     <comment ref="B38" authorId="0">
       <text>
         <r>
-          <t>student_id:f8cf3eb1-0c0a-4b95-a922-f2420c763f4a</t>
+          <t>student_id:0249bb18-663d-4e24-8434-2e4d2ade5bac</t>
         </r>
       </text>
     </comment>
     <comment ref="B39" authorId="0">
       <text>
         <r>
-          <t>student_id:6171bac6-1027-4242-b1c7-e7d6c06ba6fa</t>
+          <t>student_id:9a762dcc-0f03-41b4-9dfa-98fd9988b2d0</t>
         </r>
       </text>
     </comment>
     <comment ref="B40" authorId="0">
       <text>
         <r>
-          <t>student_id:ad19b0bc-9f77-4012-ba41-7e32ad3c6755</t>
+          <t>student_id:dbb0fc89-90a4-4873-865b-7a4be58c036a</t>
         </r>
       </text>
     </comment>
     <comment ref="B41" authorId="0">
       <text>
         <r>
-          <t>student_id:d561a6ac-414a-484c-ab7e-89323186b28d</t>
+          <t>student_id:7ece9a1f-b5d9-4468-bc47-9ee9d2b37230</t>
         </r>
       </text>
     </comment>
     <comment ref="B42" authorId="0">
       <text>
         <r>
-          <t>student_id:4103af1d-20c9-4c6f-a3dd-926698bcf9a8</t>
+          <t>student_id:06d664f5-4b4c-42bc-8339-3a54b1a56a6a</t>
         </r>
       </text>
     </comment>
     <comment ref="B43" authorId="0">
       <text>
         <r>
-          <t>student_id:269f7a85-70b1-4e8e-9970-51e37e557014</t>
+          <t>student_id:429b4d12-cf14-4df6-8890-9b4e3f9fae88</t>
         </r>
       </text>
     </comment>
     <comment ref="B44" authorId="0">
       <text>
         <r>
-          <t>student_id:6cd3e690-e5a3-4042-ba10-1ebfc50faaca</t>
+          <t>student_id:1afa993a-6d5c-4fcd-bd62-3337db7da91e</t>
         </r>
       </text>
     </comment>
     <comment ref="B45" authorId="0">
       <text>
         <r>
-          <t>student_id:7adb7526-0d4b-4cb8-aef3-ddda9b271972</t>
+          <t>student_id:14649d49-d02f-4ffe-8413-3636d970993f</t>
         </r>
       </text>
     </comment>
     <comment ref="B46" authorId="0">
       <text>
         <r>
-          <t>student_id:19721e18-0632-401e-9034-f9cfff42aa32</t>
+          <t>student_id:5aeac08c-8aef-4769-b7cf-84cef4e36502</t>
         </r>
       </text>
     </comment>
     <comment ref="B47" authorId="0">
       <text>
         <r>
-          <t>student_id:8bf06b54-9452-48c3-a532-2e263af8d777</t>
+          <t>student_id:2bebd994-b3cc-4ebb-b75f-86f236b251e3</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B48" authorId="0">
+      <text>
+        <r>
+          <t>student_id:b3b27dff-4c8c-4ee1-833a-8276646dea82</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B49" authorId="0">
+      <text>
+        <r>
+          <t>student_id:13d12863-e7a6-4874-a5ea-b604374ef728</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B50" authorId="0">
+      <text>
+        <r>
+          <t>student_id:f05301f9-5788-4220-a2b9-44b93b0bf494</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B51" authorId="0">
+      <text>
+        <r>
+          <t>student_id:99fe4e12-9127-4882-91c5-0db43603f904</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B52" authorId="0">
+      <text>
+        <r>
+          <t>student_id:05ff707a-cb46-46df-b98d-4f6ba8c71bbe</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B53" authorId="0">
+      <text>
+        <r>
+          <t>student_id:88308d27-01df-4e38-a06f-16c5e1be238a</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B54" authorId="0">
+      <text>
+        <r>
+          <t>student_id:1278c630-1c0e-409e-b989-945fc5b47f56</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B55" authorId="0">
+      <text>
+        <r>
+          <t>student_id:3d8011c4-fdfe-49d3-8e2b-c9a83fdf406e</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B56" authorId="0">
+      <text>
+        <r>
+          <t>student_id:a00f7cad-12f6-47ee-be24-04b6d0aea38e</t>
         </r>
       </text>
     </comment>
@@ -323,7 +386,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="72">
   <si>
     <t>زهراوي ادبي 2  |  AMPHI  |  BAC  |  زهراوي</t>
   </si>
@@ -346,7 +409,7 @@
     <t>الاسم واللقب</t>
   </si>
   <si>
-    <t>05/09/2026</t>
+    <t>26/09/2026</t>
   </si>
   <si>
     <t/>
@@ -355,105 +418,99 @@
     <t>معمري ريتاج</t>
   </si>
   <si>
+    <t>بريك ادم</t>
+  </si>
+  <si>
+    <t>بخوش ريتاج</t>
+  </si>
+  <si>
+    <t>سعيودي معاذ</t>
+  </si>
+  <si>
+    <t>بن عطاالله لجين</t>
+  </si>
+  <si>
+    <t>بن داود سيرين</t>
+  </si>
+  <si>
+    <t>قطش محمد</t>
+  </si>
+  <si>
+    <t>بولعتروس محمد</t>
+  </si>
+  <si>
+    <t>مفرج شروق</t>
+  </si>
+  <si>
     <t>بن دهان مرتضى</t>
   </si>
   <si>
+    <t>بو العلوة ملاك</t>
+  </si>
+  <si>
+    <t>كنيوش سديل</t>
+  </si>
+  <si>
+    <t>اوشن سندس</t>
+  </si>
+  <si>
+    <t>عكوش محمد</t>
+  </si>
+  <si>
+    <t>مجمج سندس</t>
+  </si>
+  <si>
+    <t>بوضياف نهال</t>
+  </si>
+  <si>
+    <t>بن جاب الله لينة</t>
+  </si>
+  <si>
+    <t>سعدوني يحيى</t>
+  </si>
+  <si>
+    <t>بن عثمان رتاج</t>
+  </si>
+  <si>
+    <t>بوفلعاص شاهين</t>
+  </si>
+  <si>
+    <t>صدراتي مهند</t>
+  </si>
+  <si>
+    <t>بلقاضي الاء</t>
+  </si>
+  <si>
+    <t>زواغي اية نور</t>
+  </si>
+  <si>
+    <t>بهناس ادم</t>
+  </si>
+  <si>
+    <t>زهاني رحمة</t>
+  </si>
+  <si>
+    <t>بومزبر رشا</t>
+  </si>
+  <si>
+    <t>بن سويبط ملاك</t>
+  </si>
+  <si>
+    <t>بارش بشرى</t>
+  </si>
+  <si>
+    <t>طراد مريم</t>
+  </si>
+  <si>
+    <t>لكحل سمية</t>
+  </si>
+  <si>
+    <t>مشلوخ هبة</t>
+  </si>
+  <si>
     <t>قاسمي رنيم</t>
   </si>
   <si>
-    <t>سعدوني يحيى</t>
-  </si>
-  <si>
-    <t>ناصر سيرين</t>
-  </si>
-  <si>
-    <t>بن داود سيرين</t>
-  </si>
-  <si>
-    <t>بريك ادم</t>
-  </si>
-  <si>
-    <t>بخوش ريتاج</t>
-  </si>
-  <si>
-    <t>سعيودي معاذ</t>
-  </si>
-  <si>
-    <t>بن عطاالله لجين</t>
-  </si>
-  <si>
-    <t>قطش محمد</t>
-  </si>
-  <si>
-    <t>كتاب ميليسا</t>
-  </si>
-  <si>
-    <t>بولعتروس محمد</t>
-  </si>
-  <si>
-    <t>دلوش ملاك</t>
-  </si>
-  <si>
-    <t>مفرج شروق</t>
-  </si>
-  <si>
-    <t>بو العلوة ملاك</t>
-  </si>
-  <si>
-    <t>كنيوش سديل</t>
-  </si>
-  <si>
-    <t>اوشن سندس</t>
-  </si>
-  <si>
-    <t>عكوش محمد</t>
-  </si>
-  <si>
-    <t>بوضياف نهال</t>
-  </si>
-  <si>
-    <t>بن جاب الله لينة</t>
-  </si>
-  <si>
-    <t>بن عثمان رتاج</t>
-  </si>
-  <si>
-    <t>بوفلعاص شاهين</t>
-  </si>
-  <si>
-    <t>صدراتي مهند</t>
-  </si>
-  <si>
-    <t>بلقاضي الاء</t>
-  </si>
-  <si>
-    <t>زواغي اية نور</t>
-  </si>
-  <si>
-    <t>بهناس ادم</t>
-  </si>
-  <si>
-    <t>زهاني رحمة</t>
-  </si>
-  <si>
-    <t>بومزبر رشا</t>
-  </si>
-  <si>
-    <t>بن سويبط ملاك</t>
-  </si>
-  <si>
-    <t>بارش بشرى</t>
-  </si>
-  <si>
-    <t>طراد مريم</t>
-  </si>
-  <si>
-    <t>لكحل سمية</t>
-  </si>
-  <si>
-    <t>مشلوخ هبة</t>
-  </si>
-  <si>
     <t>غجاتي يقين</t>
   </si>
   <si>
@@ -466,6 +523,9 @@
     <t>امحمد معاذ</t>
   </si>
   <si>
+    <t>كاتب ميليسا</t>
+  </si>
+  <si>
     <t>طشطاش شروق</t>
   </si>
   <si>
@@ -479,6 +539,36 @@
   </si>
   <si>
     <t>مساهل عبد النور</t>
+  </si>
+  <si>
+    <t>قويسم ايمان</t>
+  </si>
+  <si>
+    <t>جابر قصي</t>
+  </si>
+  <si>
+    <t>رامول مريم ابتول</t>
+  </si>
+  <si>
+    <t>عيساني خديجة</t>
+  </si>
+  <si>
+    <t>حسيدي رحمة</t>
+  </si>
+  <si>
+    <t>شايب سلسبيل</t>
+  </si>
+  <si>
+    <t>بركان تاج</t>
+  </si>
+  <si>
+    <t>بركان امينة</t>
+  </si>
+  <si>
+    <t>بن زاوش مريم</t>
+  </si>
+  <si>
+    <t>بن غزال محمد نزار</t>
   </si>
   <si>
     <t>تعليمات ملء الحضور والكتب / Instructions</t>
@@ -998,7 +1088,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N47"/>
+  <dimension ref="A1:N56"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -1123,7 +1213,7 @@
     </row>
     <row r="5" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>49</v>
+        <v>232</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>9</v>
@@ -1167,7 +1257,7 @@
     </row>
     <row r="6" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>54</v>
+        <v>267</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>10</v>
@@ -1211,7 +1301,7 @@
     </row>
     <row r="7" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>56</v>
+        <v>269</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>11</v>
@@ -1255,7 +1345,7 @@
     </row>
     <row r="8" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>57</v>
+        <v>271</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>12</v>
@@ -1299,7 +1389,7 @@
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>60</v>
+        <v>272</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>13</v>
@@ -1343,7 +1433,7 @@
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>14</v>
@@ -1387,7 +1477,7 @@
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <v>482</v>
+        <v>276</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>15</v>
@@ -1431,7 +1521,7 @@
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <v>484</v>
+        <v>283</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>16</v>
@@ -1475,7 +1565,7 @@
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <v>486</v>
+        <v>298</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>17</v>
@@ -1519,7 +1609,7 @@
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <v>487</v>
+        <v>299</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>18</v>
@@ -1563,7 +1653,7 @@
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
-        <v>490</v>
+        <v>300</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>19</v>
@@ -1607,7 +1697,7 @@
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
-        <v>492</v>
+        <v>301</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>20</v>
@@ -1651,7 +1741,7 @@
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
-        <v>497</v>
+        <v>302</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>21</v>
@@ -1695,7 +1785,7 @@
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
-        <v>501</v>
+        <v>303</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>22</v>
@@ -1739,7 +1829,7 @@
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
-        <v>505</v>
+        <v>304</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>23</v>
@@ -1783,7 +1873,7 @@
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
-        <v>506</v>
+        <v>305</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>24</v>
@@ -1827,7 +1917,7 @@
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
-        <v>507</v>
+        <v>306</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>25</v>
@@ -1871,7 +1961,7 @@
     </row>
     <row r="22" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
-        <v>508</v>
+        <v>307</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>26</v>
@@ -1915,7 +2005,7 @@
     </row>
     <row r="23" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
-        <v>509</v>
+        <v>308</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>27</v>
@@ -1959,7 +2049,7 @@
     </row>
     <row r="24" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
-        <v>510</v>
+        <v>309</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>28</v>
@@ -2003,7 +2093,7 @@
     </row>
     <row r="25" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
-        <v>511</v>
+        <v>310</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>29</v>
@@ -2047,7 +2137,7 @@
     </row>
     <row r="26" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
-        <v>512</v>
+        <v>311</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>30</v>
@@ -2091,7 +2181,7 @@
     </row>
     <row r="27" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
-        <v>513</v>
+        <v>312</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>31</v>
@@ -2135,7 +2225,7 @@
     </row>
     <row r="28" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
-        <v>514</v>
+        <v>313</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>32</v>
@@ -2179,7 +2269,7 @@
     </row>
     <row r="29" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
-        <v>515</v>
+        <v>314</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>33</v>
@@ -2223,7 +2313,7 @@
     </row>
     <row r="30" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
-        <v>516</v>
+        <v>315</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>34</v>
@@ -2267,7 +2357,7 @@
     </row>
     <row r="31" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
-        <v>517</v>
+        <v>316</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>35</v>
@@ -2311,7 +2401,7 @@
     </row>
     <row r="32" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
-        <v>518</v>
+        <v>317</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>36</v>
@@ -2355,7 +2445,7 @@
     </row>
     <row r="33" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
-        <v>519</v>
+        <v>318</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>37</v>
@@ -2399,7 +2489,7 @@
     </row>
     <row r="34" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
-        <v>520</v>
+        <v>319</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>38</v>
@@ -2443,7 +2533,7 @@
     </row>
     <row r="35" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
-        <v>521</v>
+        <v>320</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>39</v>
@@ -2487,7 +2577,7 @@
     </row>
     <row r="36" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
-        <v>522</v>
+        <v>321</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>40</v>
@@ -2531,7 +2621,7 @@
     </row>
     <row r="37" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
-        <v>523</v>
+        <v>322</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>41</v>
@@ -2575,7 +2665,7 @@
     </row>
     <row r="38" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
-        <v>524</v>
+        <v>323</v>
       </c>
       <c r="B38" s="7" t="s">
         <v>42</v>
@@ -2619,7 +2709,7 @@
     </row>
     <row r="39" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
-        <v>525</v>
+        <v>324</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>43</v>
@@ -2663,7 +2753,7 @@
     </row>
     <row r="40" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
-        <v>526</v>
+        <v>325</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>44</v>
@@ -2707,7 +2797,7 @@
     </row>
     <row r="41" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
-        <v>527</v>
+        <v>326</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>45</v>
@@ -2751,7 +2841,7 @@
     </row>
     <row r="42" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
-        <v>528</v>
+        <v>327</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>46</v>
@@ -2795,7 +2885,7 @@
     </row>
     <row r="43" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
-        <v>529</v>
+        <v>328</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>47</v>
@@ -2839,7 +2929,7 @@
     </row>
     <row r="44" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
-        <v>530</v>
+        <v>329</v>
       </c>
       <c r="B44" s="7" t="s">
         <v>48</v>
@@ -2883,7 +2973,7 @@
     </row>
     <row r="45" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
-        <v>531</v>
+        <v>330</v>
       </c>
       <c r="B45" s="7" t="s">
         <v>49</v>
@@ -2927,7 +3017,7 @@
     </row>
     <row r="46" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
-        <v>532</v>
+        <v>331</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>50</v>
@@ -2971,7 +3061,7 @@
     </row>
     <row r="47" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
-        <v>533</v>
+        <v>332</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>51</v>
@@ -3010,6 +3100,402 @@
         <v>0</v>
       </c>
       <c r="N47" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A48" s="6">
+        <v>333</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C48" s="9">
+        <v>0</v>
+      </c>
+      <c r="D48" s="9">
+        <v>0</v>
+      </c>
+      <c r="E48" s="9">
+        <v>0</v>
+      </c>
+      <c r="F48" s="9">
+        <v>0</v>
+      </c>
+      <c r="G48" s="9">
+        <v>0</v>
+      </c>
+      <c r="H48" s="9">
+        <v>0</v>
+      </c>
+      <c r="I48" s="9">
+        <v>0</v>
+      </c>
+      <c r="J48" s="9">
+        <v>0</v>
+      </c>
+      <c r="K48" s="9">
+        <v>0</v>
+      </c>
+      <c r="L48" s="9">
+        <v>0</v>
+      </c>
+      <c r="M48" s="9">
+        <v>0</v>
+      </c>
+      <c r="N48" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A49" s="6">
+        <v>334</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C49" s="8">
+        <v>0</v>
+      </c>
+      <c r="D49" s="8">
+        <v>0</v>
+      </c>
+      <c r="E49" s="8">
+        <v>0</v>
+      </c>
+      <c r="F49" s="8">
+        <v>0</v>
+      </c>
+      <c r="G49" s="8">
+        <v>0</v>
+      </c>
+      <c r="H49" s="8">
+        <v>0</v>
+      </c>
+      <c r="I49" s="8">
+        <v>0</v>
+      </c>
+      <c r="J49" s="8">
+        <v>0</v>
+      </c>
+      <c r="K49" s="8">
+        <v>0</v>
+      </c>
+      <c r="L49" s="8">
+        <v>0</v>
+      </c>
+      <c r="M49" s="8">
+        <v>0</v>
+      </c>
+      <c r="N49" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A50" s="6">
+        <v>335</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C50" s="9">
+        <v>0</v>
+      </c>
+      <c r="D50" s="9">
+        <v>0</v>
+      </c>
+      <c r="E50" s="9">
+        <v>0</v>
+      </c>
+      <c r="F50" s="9">
+        <v>0</v>
+      </c>
+      <c r="G50" s="9">
+        <v>0</v>
+      </c>
+      <c r="H50" s="9">
+        <v>0</v>
+      </c>
+      <c r="I50" s="9">
+        <v>0</v>
+      </c>
+      <c r="J50" s="9">
+        <v>0</v>
+      </c>
+      <c r="K50" s="9">
+        <v>0</v>
+      </c>
+      <c r="L50" s="9">
+        <v>0</v>
+      </c>
+      <c r="M50" s="9">
+        <v>0</v>
+      </c>
+      <c r="N50" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A51" s="6">
+        <v>336</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C51" s="8">
+        <v>0</v>
+      </c>
+      <c r="D51" s="8">
+        <v>0</v>
+      </c>
+      <c r="E51" s="8">
+        <v>0</v>
+      </c>
+      <c r="F51" s="8">
+        <v>0</v>
+      </c>
+      <c r="G51" s="8">
+        <v>0</v>
+      </c>
+      <c r="H51" s="8">
+        <v>0</v>
+      </c>
+      <c r="I51" s="8">
+        <v>0</v>
+      </c>
+      <c r="J51" s="8">
+        <v>0</v>
+      </c>
+      <c r="K51" s="8">
+        <v>0</v>
+      </c>
+      <c r="L51" s="8">
+        <v>0</v>
+      </c>
+      <c r="M51" s="8">
+        <v>0</v>
+      </c>
+      <c r="N51" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A52" s="6">
+        <v>337</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C52" s="9">
+        <v>0</v>
+      </c>
+      <c r="D52" s="9">
+        <v>0</v>
+      </c>
+      <c r="E52" s="9">
+        <v>0</v>
+      </c>
+      <c r="F52" s="9">
+        <v>0</v>
+      </c>
+      <c r="G52" s="9">
+        <v>0</v>
+      </c>
+      <c r="H52" s="9">
+        <v>0</v>
+      </c>
+      <c r="I52" s="9">
+        <v>0</v>
+      </c>
+      <c r="J52" s="9">
+        <v>0</v>
+      </c>
+      <c r="K52" s="9">
+        <v>0</v>
+      </c>
+      <c r="L52" s="9">
+        <v>0</v>
+      </c>
+      <c r="M52" s="9">
+        <v>0</v>
+      </c>
+      <c r="N52" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A53" s="6">
+        <v>338</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C53" s="8">
+        <v>0</v>
+      </c>
+      <c r="D53" s="8">
+        <v>0</v>
+      </c>
+      <c r="E53" s="8">
+        <v>0</v>
+      </c>
+      <c r="F53" s="8">
+        <v>0</v>
+      </c>
+      <c r="G53" s="8">
+        <v>0</v>
+      </c>
+      <c r="H53" s="8">
+        <v>0</v>
+      </c>
+      <c r="I53" s="8">
+        <v>0</v>
+      </c>
+      <c r="J53" s="8">
+        <v>0</v>
+      </c>
+      <c r="K53" s="8">
+        <v>0</v>
+      </c>
+      <c r="L53" s="8">
+        <v>0</v>
+      </c>
+      <c r="M53" s="8">
+        <v>0</v>
+      </c>
+      <c r="N53" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A54" s="6">
+        <v>339</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C54" s="9">
+        <v>0</v>
+      </c>
+      <c r="D54" s="9">
+        <v>0</v>
+      </c>
+      <c r="E54" s="9">
+        <v>0</v>
+      </c>
+      <c r="F54" s="9">
+        <v>0</v>
+      </c>
+      <c r="G54" s="9">
+        <v>0</v>
+      </c>
+      <c r="H54" s="9">
+        <v>0</v>
+      </c>
+      <c r="I54" s="9">
+        <v>0</v>
+      </c>
+      <c r="J54" s="9">
+        <v>0</v>
+      </c>
+      <c r="K54" s="9">
+        <v>0</v>
+      </c>
+      <c r="L54" s="9">
+        <v>0</v>
+      </c>
+      <c r="M54" s="9">
+        <v>0</v>
+      </c>
+      <c r="N54" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A55" s="6">
+        <v>340</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C55" s="8">
+        <v>0</v>
+      </c>
+      <c r="D55" s="8">
+        <v>0</v>
+      </c>
+      <c r="E55" s="8">
+        <v>0</v>
+      </c>
+      <c r="F55" s="8">
+        <v>0</v>
+      </c>
+      <c r="G55" s="8">
+        <v>0</v>
+      </c>
+      <c r="H55" s="8">
+        <v>0</v>
+      </c>
+      <c r="I55" s="8">
+        <v>0</v>
+      </c>
+      <c r="J55" s="8">
+        <v>0</v>
+      </c>
+      <c r="K55" s="8">
+        <v>0</v>
+      </c>
+      <c r="L55" s="8">
+        <v>0</v>
+      </c>
+      <c r="M55" s="8">
+        <v>0</v>
+      </c>
+      <c r="N55" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A56" s="6">
+        <v>341</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C56" s="9">
+        <v>0</v>
+      </c>
+      <c r="D56" s="9">
+        <v>0</v>
+      </c>
+      <c r="E56" s="9">
+        <v>0</v>
+      </c>
+      <c r="F56" s="9">
+        <v>0</v>
+      </c>
+      <c r="G56" s="9">
+        <v>0</v>
+      </c>
+      <c r="H56" s="9">
+        <v>0</v>
+      </c>
+      <c r="I56" s="9">
+        <v>0</v>
+      </c>
+      <c r="J56" s="9">
+        <v>0</v>
+      </c>
+      <c r="K56" s="9">
+        <v>0</v>
+      </c>
+      <c r="L56" s="9">
+        <v>0</v>
+      </c>
+      <c r="M56" s="9">
+        <v>0</v>
+      </c>
+      <c r="N56" s="9">
         <v>0</v>
       </c>
     </row>
@@ -3037,7 +3523,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -3047,12 +3533,12 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
@@ -3062,27 +3548,27 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
@@ -3092,12 +3578,12 @@
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
@@ -3107,7 +3593,7 @@
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/data/attendance/AMPHI_زهراوي_ادبي_2.xlsx
+++ b/data/attendance/AMPHI_زهراوي_ادبي_2.xlsx
@@ -3,9 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
-  <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
-  </bookViews>
   <sheets>
     <sheet sheetId="1" name="Présences" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="📖 Instructions" state="visible" r:id="rId5"/>
@@ -23,13 +20,6 @@
     <comment ref="B5" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:17558c2a-1262-434a-97e3-56eca8a756b1</t>
         </r>
       </text>
@@ -37,13 +27,6 @@
     <comment ref="B6" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:1e892613-fb1a-4dd7-a7d8-8e2170bc0d4e</t>
         </r>
       </text>
@@ -51,13 +34,6 @@
     <comment ref="B7" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:f1624681-c1a7-4737-b428-f389d7cdc975</t>
         </r>
       </text>
@@ -65,13 +41,6 @@
     <comment ref="B8" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:0b7d12e6-cea4-4861-805e-d2a4cac3ec51</t>
         </r>
       </text>
@@ -79,13 +48,6 @@
     <comment ref="B9" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:ed42b87b-c4b3-4fff-98a5-a5156af6f689</t>
         </r>
       </text>
@@ -93,13 +55,6 @@
     <comment ref="B10" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:11e09847-4fe5-437d-89d7-80b103ce05a7</t>
         </r>
       </text>
@@ -107,13 +62,6 @@
     <comment ref="B11" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:b3ac5a70-f136-4fbd-ba38-0f00712e5362</t>
         </r>
       </text>
@@ -121,13 +69,6 @@
     <comment ref="B12" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:99a6b5eb-f8ef-42f7-9d8d-450be69cbcf3</t>
         </r>
       </text>
@@ -135,13 +76,6 @@
     <comment ref="B13" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:ee2da73d-8c46-4332-a76e-81eac4fbf687</t>
         </r>
       </text>
@@ -149,13 +83,6 @@
     <comment ref="B14" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:44b5cb5d-f5f3-40f1-a42d-2a355c517e79</t>
         </r>
       </text>
@@ -163,13 +90,6 @@
     <comment ref="B15" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:be0915c3-3f34-422b-b71d-114f720f0ff9</t>
         </r>
       </text>
@@ -177,13 +97,6 @@
     <comment ref="B16" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:4a2c6443-9485-4beb-a1e1-79dba040809f</t>
         </r>
       </text>
@@ -191,13 +104,6 @@
     <comment ref="B17" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:1937ad56-0494-4a16-8e8e-e38bd86eab28</t>
         </r>
       </text>
@@ -205,13 +111,6 @@
     <comment ref="B18" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:216b6e1b-5c35-446f-90eb-0b3769c3c745</t>
         </r>
       </text>
@@ -219,13 +118,6 @@
     <comment ref="B19" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:50589b50-f0a9-431d-b668-7693580bd713</t>
         </r>
       </text>
@@ -233,13 +125,6 @@
     <comment ref="B20" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:f5e9ee37-b4b0-43ce-906e-abd54c789347</t>
         </r>
       </text>
@@ -247,13 +132,6 @@
     <comment ref="B21" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:fc3694ad-1ef1-4dfb-a3ff-ade61864b818</t>
         </r>
       </text>
@@ -261,13 +139,6 @@
     <comment ref="B22" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:ac87ac71-9fcb-4f92-bef9-33417995d6ec</t>
         </r>
       </text>
@@ -275,13 +146,6 @@
     <comment ref="B23" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:d4541bbb-072f-4861-a46c-930b232417f4</t>
         </r>
       </text>
@@ -289,13 +153,6 @@
     <comment ref="B24" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:f8454c66-d041-4f71-854a-1897e725f844</t>
         </r>
       </text>
@@ -303,13 +160,6 @@
     <comment ref="B25" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:6f278547-d060-4238-9749-f231d68329be</t>
         </r>
       </text>
@@ -317,13 +167,6 @@
     <comment ref="B26" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:635645e8-e183-4792-af28-708262cebe45</t>
         </r>
       </text>
@@ -331,13 +174,6 @@
     <comment ref="B27" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:faea8b09-9503-4c4c-814f-2de6581ee480</t>
         </r>
       </text>
@@ -345,13 +181,6 @@
     <comment ref="B28" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:f0f526ab-f4c2-4859-bd2a-a157bafd0908</t>
         </r>
       </text>
@@ -359,13 +188,6 @@
     <comment ref="B29" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:608cad76-2f39-4367-ac8a-aa8be715f677</t>
         </r>
       </text>
@@ -373,13 +195,6 @@
     <comment ref="B30" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:0ce281db-d0ce-4744-ad3e-b6f061a198a9</t>
         </r>
       </text>
@@ -387,13 +202,6 @@
     <comment ref="B31" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:ec9b824b-718b-4fbd-9e89-239ba201a33e</t>
         </r>
       </text>
@@ -401,13 +209,6 @@
     <comment ref="B32" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:d0763c0b-bc02-4a69-82be-2fd3386f470a</t>
         </r>
       </text>
@@ -415,13 +216,6 @@
     <comment ref="B33" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:78ea45ba-95ee-455a-a124-6c967b6f6953</t>
         </r>
       </text>
@@ -429,13 +223,6 @@
     <comment ref="B34" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:3ebf1dfc-9076-4122-a2dc-43b6b1e9c0fe</t>
         </r>
       </text>
@@ -443,13 +230,6 @@
     <comment ref="B35" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:31fe298a-ac2e-453f-b6c1-d1745c5e3e59</t>
         </r>
       </text>
@@ -457,13 +237,6 @@
     <comment ref="B36" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:d22b3e6b-1630-40f5-91b3-7b6fc7e4ad05</t>
         </r>
       </text>
@@ -471,13 +244,6 @@
     <comment ref="B37" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:b2a65661-2ddd-4d8d-9070-9e268765452b</t>
         </r>
       </text>
@@ -485,13 +251,6 @@
     <comment ref="B38" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:0249bb18-663d-4e24-8434-2e4d2ade5bac</t>
         </r>
       </text>
@@ -499,13 +258,6 @@
     <comment ref="B39" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:9a762dcc-0f03-41b4-9dfa-98fd9988b2d0</t>
         </r>
       </text>
@@ -513,13 +265,6 @@
     <comment ref="B40" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:dbb0fc89-90a4-4873-865b-7a4be58c036a</t>
         </r>
       </text>
@@ -527,13 +272,6 @@
     <comment ref="B41" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:7ece9a1f-b5d9-4468-bc47-9ee9d2b37230</t>
         </r>
       </text>
@@ -541,13 +279,6 @@
     <comment ref="B42" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:06d664f5-4b4c-42bc-8339-3a54b1a56a6a</t>
         </r>
       </text>
@@ -555,13 +286,6 @@
     <comment ref="B43" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:429b4d12-cf14-4df6-8890-9b4e3f9fae88</t>
         </r>
       </text>
@@ -569,13 +293,6 @@
     <comment ref="B44" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:1afa993a-6d5c-4fcd-bd62-3337db7da91e</t>
         </r>
       </text>
@@ -583,13 +300,6 @@
     <comment ref="B45" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:14649d49-d02f-4ffe-8413-3636d970993f</t>
         </r>
       </text>
@@ -597,13 +307,6 @@
     <comment ref="B46" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:5aeac08c-8aef-4769-b7cf-84cef4e36502</t>
         </r>
       </text>
@@ -611,13 +314,6 @@
     <comment ref="B47" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:2bebd994-b3cc-4ebb-b75f-86f236b251e3</t>
         </r>
       </text>
@@ -625,13 +321,6 @@
     <comment ref="B48" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:b3b27dff-4c8c-4ee1-833a-8276646dea82</t>
         </r>
       </text>
@@ -639,13 +328,6 @@
     <comment ref="B49" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:13d12863-e7a6-4874-a5ea-b604374ef728</t>
         </r>
       </text>
@@ -653,97 +335,41 @@
     <comment ref="B50" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>student_id:f05301f9-5788-4220-a2b9-44b93b0bf494</t>
+          <t>student_id:99fe4e12-9127-4882-91c5-0db43603f904</t>
         </r>
       </text>
     </comment>
     <comment ref="B51" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>student_id:99fe4e12-9127-4882-91c5-0db43603f904</t>
+          <t>student_id:05ff707a-cb46-46df-b98d-4f6ba8c71bbe</t>
         </r>
       </text>
     </comment>
     <comment ref="B52" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>student_id:05ff707a-cb46-46df-b98d-4f6ba8c71bbe</t>
+          <t>student_id:88308d27-01df-4e38-a06f-16c5e1be238a</t>
         </r>
       </text>
     </comment>
     <comment ref="B53" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>student_id:88308d27-01df-4e38-a06f-16c5e1be238a</t>
+          <t>student_id:1278c630-1c0e-409e-b989-945fc5b47f56</t>
         </r>
       </text>
     </comment>
     <comment ref="B54" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>student_id:1278c630-1c0e-409e-b989-945fc5b47f56</t>
+          <t>student_id:3d8011c4-fdfe-49d3-8e2b-c9a83fdf406e</t>
         </r>
       </text>
     </comment>
     <comment ref="B55" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>student_id:3d8011c4-fdfe-49d3-8e2b-c9a83fdf406e</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B56" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:a00f7cad-12f6-47ee-be24-04b6d0aea38e</t>
         </r>
       </text>
@@ -753,7 +379,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="76">
   <si>
     <t>زهراوي ادبي 2  |  AMPHI  |  BAC  |  زهراوي</t>
   </si>
@@ -767,6 +393,9 @@
     <t>has_books=false</t>
   </si>
   <si>
+    <t>is_formation=false</t>
+  </si>
+  <si>
     <t>حصة مجانية؟ (1 = نعم / 0 = عادية)</t>
   </si>
   <si>
@@ -785,6 +414,9 @@
     <t>26/09/2026</t>
   </si>
   <si>
+    <t>03/10/2026</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -923,9 +555,6 @@
     <t>رامول مريم ابتول</t>
   </si>
   <si>
-    <t>عيساني خديجة</t>
-  </si>
-  <si>
     <t>حسيدي رحمة</t>
   </si>
   <si>
@@ -971,7 +600,10 @@
     <t>3. للأفواج التي لها كتب (ت1 / ت2 / ت3) :</t>
   </si>
   <si>
-    <t xml:space="preserve">   → اكتب 1 في خانة الفصل إذا استلم الطالب كتابه، أو 0 إذا لم يستلم</t>
+    <t xml:space="preserve">   → للأفواج التي لها كتابان في هذا الفصل (ت1): تم توفير عمودين (كتاب 1 ت 1 و كتاب 2 ت 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   → اكتب 1 (أو X) في خانة الكتاب إذا استلم الطالب نسخته، أو 0 إذا لم يستلم</t>
   </si>
   <si>
     <t>4. احفظ الملف (Ctrl+S) بعد الانتهاء ثم شغّل أمر الاستيراد.</t>
@@ -993,40 +625,33 @@
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="13"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FFC00000"/>
       <sz val="9"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FFC00000"/>
       <sz val="10"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="10"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <color rgb="FF666666"/>
+      <color rgb="666666"/>
       <sz val="9"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="9">
@@ -1113,7 +738,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1468,15 +1093,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N56"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N55"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="14" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1494,7 +1119,7 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
     </row>
-    <row r="2" hidden="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" hidden="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1504,10 +1129,13 @@
       <c r="C2" t="s">
         <v>3</v>
       </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="3">
@@ -1549,63 +1177,63 @@
     </row>
     <row r="4" ht="42" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>232</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C5" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="8">
         <v>0</v>
@@ -1635,21 +1263,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>267</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C6" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="9">
         <v>0</v>
@@ -1679,12 +1307,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>269</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C7" s="8">
         <v>0</v>
@@ -1693,7 +1321,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="8">
         <v>0</v>
@@ -1723,21 +1351,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>271</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C8" s="9">
         <v>0</v>
       </c>
       <c r="D8" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="9">
         <v>0</v>
@@ -1767,21 +1395,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>272</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C9" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="8">
         <v>0</v>
@@ -1811,21 +1439,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>273</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C10" s="9">
         <v>0</v>
       </c>
       <c r="D10" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" s="9">
         <v>0</v>
@@ -1855,21 +1483,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>276</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C11" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" s="8">
         <v>0</v>
@@ -1899,21 +1527,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>283</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C12" s="9">
         <v>0</v>
       </c>
       <c r="D12" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" s="9">
         <v>0</v>
@@ -1943,21 +1571,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>298</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C13" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" s="8">
         <v>0</v>
@@ -1987,21 +1615,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>299</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C14" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="9">
         <v>0</v>
@@ -2031,21 +1659,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>300</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C15" s="8">
         <v>0</v>
       </c>
       <c r="D15" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" s="8">
         <v>0</v>
@@ -2075,21 +1703,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>301</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C16" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" s="9">
         <v>0</v>
@@ -2119,21 +1747,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>302</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C17" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" s="8">
         <v>0</v>
@@ -2163,21 +1791,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>303</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C18" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" s="9">
         <v>0</v>
@@ -2207,21 +1835,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>304</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C19" s="8">
         <v>0</v>
       </c>
       <c r="D19" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" s="8">
         <v>0</v>
@@ -2251,21 +1879,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>305</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C20" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" s="9">
         <v>0</v>
@@ -2295,21 +1923,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>306</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C21" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21" s="8">
         <v>0</v>
@@ -2339,21 +1967,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>307</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C22" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22" s="9">
         <v>0</v>
@@ -2383,21 +2011,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>308</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C23" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" s="8">
         <v>0</v>
@@ -2427,21 +2055,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>309</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C24" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24" s="9">
         <v>0</v>
@@ -2471,21 +2099,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>310</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C25" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25" s="8">
         <v>0</v>
@@ -2515,21 +2143,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>311</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C26" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" s="9">
         <v>0</v>
@@ -2559,21 +2187,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>312</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C27" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27" s="8">
         <v>0</v>
@@ -2603,21 +2231,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>313</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C28" s="9">
         <v>0</v>
       </c>
       <c r="D28" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28" s="9">
         <v>0</v>
@@ -2647,21 +2275,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>314</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C29" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F29" s="8">
         <v>0</v>
@@ -2691,21 +2319,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>315</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C30" s="9">
         <v>0</v>
       </c>
       <c r="D30" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30" s="9">
         <v>0</v>
@@ -2735,21 +2363,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>316</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C31" s="8">
         <v>0</v>
       </c>
       <c r="D31" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F31" s="8">
         <v>0</v>
@@ -2779,21 +2407,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>317</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C32" s="9">
         <v>0</v>
       </c>
       <c r="D32" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F32" s="9">
         <v>0</v>
@@ -2823,21 +2451,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>318</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C33" s="8">
         <v>0</v>
       </c>
       <c r="D33" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F33" s="8">
         <v>0</v>
@@ -2867,21 +2495,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>319</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C34" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D34" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F34" s="9">
         <v>0</v>
@@ -2911,21 +2539,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>320</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C35" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D35" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E35" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F35" s="8">
         <v>0</v>
@@ -2955,21 +2583,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>321</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C36" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D36" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E36" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F36" s="9">
         <v>0</v>
@@ -2999,21 +2627,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>322</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C37" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D37" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E37" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F37" s="8">
         <v>0</v>
@@ -3043,18 +2671,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>323</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C38" s="9">
         <v>0</v>
       </c>
       <c r="D38" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E38" s="9">
         <v>0</v>
@@ -3087,21 +2715,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>324</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C39" s="8">
         <v>0</v>
       </c>
       <c r="D39" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E39" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F39" s="8">
         <v>0</v>
@@ -3131,21 +2759,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>325</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C40" s="9">
         <v>0</v>
       </c>
       <c r="D40" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E40" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F40" s="9">
         <v>0</v>
@@ -3175,21 +2803,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>326</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C41" s="8">
         <v>0</v>
       </c>
       <c r="D41" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F41" s="8">
         <v>0</v>
@@ -3219,21 +2847,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
         <v>327</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C42" s="9">
         <v>0</v>
       </c>
       <c r="D42" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E42" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42" s="9">
         <v>0</v>
@@ -3263,21 +2891,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>328</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C43" s="8">
         <v>0</v>
       </c>
       <c r="D43" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E43" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F43" s="8">
         <v>0</v>
@@ -3307,21 +2935,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
         <v>329</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C44" s="9">
         <v>0</v>
       </c>
       <c r="D44" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E44" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F44" s="9">
         <v>0</v>
@@ -3351,21 +2979,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>330</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C45" s="8">
         <v>0</v>
       </c>
       <c r="D45" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E45" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F45" s="8">
         <v>0</v>
@@ -3395,21 +3023,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
         <v>331</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C46" s="9">
         <v>0</v>
       </c>
       <c r="D46" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E46" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F46" s="9">
         <v>0</v>
@@ -3439,21 +3067,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="47" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
         <v>332</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C47" s="8">
         <v>0</v>
       </c>
       <c r="D47" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E47" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F47" s="8">
         <v>0</v>
@@ -3483,12 +3111,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="48" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
         <v>333</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C48" s="9">
         <v>0</v>
@@ -3497,7 +3125,7 @@
         <v>0</v>
       </c>
       <c r="E48" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F48" s="9">
         <v>0</v>
@@ -3527,12 +3155,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
         <v>334</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C49" s="8">
         <v>0</v>
@@ -3541,7 +3169,7 @@
         <v>0</v>
       </c>
       <c r="E49" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49" s="8">
         <v>0</v>
@@ -3571,12 +3199,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="50" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C50" s="9">
         <v>0</v>
@@ -3615,12 +3243,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="51" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C51" s="8">
         <v>0</v>
@@ -3629,7 +3257,7 @@
         <v>0</v>
       </c>
       <c r="E51" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F51" s="8">
         <v>0</v>
@@ -3659,12 +3287,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="52" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C52" s="9">
         <v>0</v>
@@ -3673,7 +3301,7 @@
         <v>0</v>
       </c>
       <c r="E52" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F52" s="9">
         <v>0</v>
@@ -3703,12 +3331,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="53" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C53" s="8">
         <v>0</v>
@@ -3717,7 +3345,7 @@
         <v>0</v>
       </c>
       <c r="E53" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F53" s="8">
         <v>0</v>
@@ -3747,12 +3375,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C54" s="9">
         <v>0</v>
@@ -3761,7 +3389,7 @@
         <v>0</v>
       </c>
       <c r="E54" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F54" s="9">
         <v>0</v>
@@ -3791,12 +3419,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C55" s="8">
         <v>0</v>
@@ -3805,7 +3433,7 @@
         <v>0</v>
       </c>
       <c r="E55" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F55" s="8">
         <v>0</v>
@@ -3832,50 +3460,6 @@
         <v>0</v>
       </c>
       <c r="N55" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A56" s="6">
-        <v>341</v>
-      </c>
-      <c r="B56" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="C56" s="9">
-        <v>0</v>
-      </c>
-      <c r="D56" s="9">
-        <v>0</v>
-      </c>
-      <c r="E56" s="9">
-        <v>1</v>
-      </c>
-      <c r="F56" s="9">
-        <v>0</v>
-      </c>
-      <c r="G56" s="9">
-        <v>0</v>
-      </c>
-      <c r="H56" s="9">
-        <v>0</v>
-      </c>
-      <c r="I56" s="9">
-        <v>0</v>
-      </c>
-      <c r="J56" s="9">
-        <v>0</v>
-      </c>
-      <c r="K56" s="9">
-        <v>0</v>
-      </c>
-      <c r="L56" s="9">
-        <v>0</v>
-      </c>
-      <c r="M56" s="9">
-        <v>0</v>
-      </c>
-      <c r="N56" s="9">
         <v>0</v>
       </c>
     </row>
@@ -3885,7 +3469,7 @@
     <mergeCell ref="A3:B3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -3895,89 +3479,94 @@
   <sheetPr>
     <tabColor rgb="FF70AD47"/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:A16"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>73</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>